--- a/EN01.xlsx
+++ b/EN01.xlsx
@@ -1241,994 +1241,688 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DF3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BX3"/>
+  <sheetFormatPr defaultRowHeight="14" ns3:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:76" s="1" customFormat="1" ns3:dyDescent="0.3">
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="DA1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="DB1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="DC1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="DD1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="DE1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="DF1" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:76" s="1" customFormat="1" ns3:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="BY2" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="BZ2" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="CA2" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="CB2" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="CC2" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="CD2" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="CE2" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="CF2" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="CG2" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="CH2" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="CI2" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="CJ2" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="CK2" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="CL2" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="CM2" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="CN2" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="CO2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="CP2" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="CQ2" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="CR2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="CS2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="CT2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="CU2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="CV2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="CW2" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="CX2" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="CY2" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="CZ2" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="DB2" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="DC2" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="DD2" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="DE2" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="DF2" s="2" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:110" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:76" s="1" customFormat="1" ns3:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B3" s="1">
-        <v>713524</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D3" s="1">
+      <c r="C3" s="1">
         <v>994029</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="E3" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
+      </c>
+      <c r="F3" s="1">
+        <v>799673</v>
+      </c>
+      <c r="G3" s="1">
+        <v>959915</v>
+      </c>
+      <c r="H3" s="1">
+        <v>755816</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J3" s="1">
-        <v>799673</v>
+        <v>946310</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="L3" s="1">
-        <v>959915</v>
+        <v>748716</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="N3" s="1">
-        <v>755816</v>
+        <v>229</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>946310</v>
+        <v>233</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>237</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="V3" s="1">
-        <v>748716</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>229</v>
+        <v>732898</v>
+      </c>
+      <c r="W3" s="1">
+        <v>324820</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>232</v>
+        <v>243</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>994116</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>411023</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>732898</v>
+        <v>253</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>910650</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="AK3" s="1">
-        <v>324820</v>
+        <v>758329</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="AN3" s="1">
-        <v>994116</v>
-      </c>
-      <c r="AO3" s="1">
-        <v>690872</v>
-      </c>
-      <c r="AP3" s="1">
-        <v>685492</v>
+        <v>257</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>712504</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>246</v>
+        <v>264</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>717797</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>248</v>
+        <v>266</v>
+      </c>
+      <c r="AU3" s="1">
+        <v>878909</v>
       </c>
       <c r="AV3" s="2" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="AX3" s="1">
-        <v>411023</v>
+        <v>986989</v>
       </c>
       <c r="AY3" s="2" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="AZ3" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="BC3" s="1">
-        <v>910650</v>
+        <v>276</v>
+      </c>
+      <c r="BA3" s="1">
+        <v>390250</v>
+      </c>
+      <c r="BB3" s="1">
+        <v>950451</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="BF3" s="1">
-        <v>758329</v>
+        <v>279</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="BG3" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="BH3" s="1">
-        <v>712504</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>258</v>
+        <v>282</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="BI3" s="1">
+        <v>697541</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>260</v>
+        <v>284</v>
+      </c>
+      <c r="BK3" s="1">
+        <v>775374</v>
       </c>
       <c r="BL3" s="2" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>263</v>
+        <v>286</v>
+      </c>
+      <c r="BN3" s="1">
+        <v>965751</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>265</v>
+        <v>287</v>
+      </c>
+      <c r="BP3" s="1">
+        <v>903577</v>
       </c>
       <c r="BQ3" s="1">
-        <v>717797</v>
+        <v>895064</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="BW3" s="1">
-        <v>878909</v>
+        <v>291</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="BX3" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="BY3" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="BZ3" s="1">
-        <v>986989</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="CC3" s="1">
-        <v>719073</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="CF3" s="1">
-        <v>390250</v>
-      </c>
-      <c r="CG3" s="1">
-        <v>950451</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="CK3" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="CL3" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="CO3" s="1">
-        <v>697541</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="CQ3" s="1">
-        <v>775374</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="CT3" s="1">
-        <v>965751</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="CV3" s="1">
-        <v>903577</v>
-      </c>
-      <c r="CW3" s="1">
-        <v>895064</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="CZ3" s="1">
-        <v>648270</v>
-      </c>
-      <c r="DB3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="DC3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="DD3" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="DE3" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="DF3" s="2" t="s">
         <v>292</v>
       </c>
     </row>
